--- a/data/QMthermoScan_H2_wB97Mp2_def2QZVPP.xlsx
+++ b/data/QMthermoScan_H2_wB97Mp2_def2QZVPP.xlsx
@@ -466,42 +466,42 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>zpe/J</t>
+          <t>zpe/(J/mol)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>U_corr/J</t>
+          <t>U_corr/(J/mol)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>H_corr/J</t>
+          <t>H_corr/(J/mol)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>G_corr/J</t>
+          <t>G_corr/(J/mol)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>ee/J</t>
+          <t>ee/(J/mol)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>U/J</t>
+          <t>U/(J/mol)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>H/J</t>
+          <t>H/(J/mol)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>G/J</t>
+          <t>G/(J/mol)</t>
         </is>
       </c>
     </row>
@@ -513,43 +513,43 @@
         <v>101325</v>
       </c>
       <c r="C2" t="n">
-        <v>2.540042246119635e+27</v>
+        <v>1.925716333514632e+29</v>
       </c>
       <c r="D2" t="n">
-        <v>40995864523887.34</v>
+        <v>1.925716333514632e+29</v>
       </c>
       <c r="E2" t="n">
-        <v>20.786162</v>
+        <v>12.4716972</v>
       </c>
       <c r="F2" t="n">
-        <v>29.1006268</v>
+        <v>20.786162</v>
       </c>
       <c r="G2" t="n">
-        <v>98.502111732679</v>
+        <v>126.1750431305657</v>
       </c>
       <c r="H2" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>28483.28763400882</v>
+        <v>1247.16972</v>
       </c>
       <c r="J2" t="n">
-        <v>29314.73411400882</v>
+        <v>2078.6162</v>
       </c>
       <c r="K2" t="n">
-        <v>19464.52294074092</v>
+        <v>-10538.88811305657</v>
       </c>
       <c r="L2" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M2" t="n">
-        <v>-3049107.895968864</v>
+        <v>-3076344.013882873</v>
       </c>
       <c r="N2" t="n">
-        <v>-3048276.449488864</v>
+        <v>-3075512.567402873</v>
       </c>
       <c r="O2" t="n">
-        <v>-3058126.660662132</v>
+        <v>-3088130.07171593</v>
       </c>
     </row>
     <row r="3">
@@ -560,43 +560,43 @@
         <v>101325</v>
       </c>
       <c r="C3" t="n">
-        <v>1.049930003492886e+28</v>
+        <v>5.306650207260884e+29</v>
       </c>
       <c r="D3" t="n">
-        <v>6.705426701600574e+18</v>
+        <v>5.306650207260884e+29</v>
       </c>
       <c r="E3" t="n">
-        <v>20.786162</v>
+        <v>12.4716972</v>
       </c>
       <c r="F3" t="n">
-        <v>29.1006268</v>
+        <v>20.786162</v>
       </c>
       <c r="G3" t="n">
-        <v>110.3013938480033</v>
+        <v>134.6031065530495</v>
       </c>
       <c r="H3" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>29522.59573400882</v>
+        <v>1870.75458</v>
       </c>
       <c r="J3" t="n">
-        <v>30769.76545400882</v>
+        <v>3117.9243</v>
       </c>
       <c r="K3" t="n">
-        <v>14224.55637680832</v>
+        <v>-17072.54168295742</v>
       </c>
       <c r="L3" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M3" t="n">
-        <v>-3048068.587868865</v>
+        <v>-3075720.429022873</v>
       </c>
       <c r="N3" t="n">
-        <v>-3046821.418148865</v>
+        <v>-3074473.259302873</v>
       </c>
       <c r="O3" t="n">
-        <v>-3063366.627226065</v>
+        <v>-3094663.72528583</v>
       </c>
     </row>
     <row r="4">
@@ -607,43 +607,43 @@
         <v>101325</v>
       </c>
       <c r="C4" t="n">
-        <v>2.873729754770452e+28</v>
+        <v>1.089349662455913e+30</v>
       </c>
       <c r="D4" t="n">
-        <v>3.650862522648575e+21</v>
+        <v>1.089349662455913e+30</v>
       </c>
       <c r="E4" t="n">
-        <v>20.78616200013534</v>
+        <v>12.4716972</v>
       </c>
       <c r="F4" t="n">
-        <v>29.10062680013534</v>
+        <v>20.786162</v>
       </c>
       <c r="G4" t="n">
-        <v>118.6731083448627</v>
+        <v>140.5829127155279</v>
       </c>
       <c r="H4" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>30561.90383400967</v>
+        <v>2494.33944</v>
       </c>
       <c r="J4" t="n">
-        <v>32224.79679400967</v>
+        <v>4157.2324</v>
       </c>
       <c r="K4" t="n">
-        <v>8490.175125037131</v>
+        <v>-23959.35014310558</v>
       </c>
       <c r="L4" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M4" t="n">
-        <v>-3047029.279768864</v>
+        <v>-3075096.844162873</v>
       </c>
       <c r="N4" t="n">
-        <v>-3045366.386808863</v>
+        <v>-3073433.951202873</v>
       </c>
       <c r="O4" t="n">
-        <v>-3069101.008477836</v>
+        <v>-3101550.533745979</v>
       </c>
     </row>
     <row r="5">
@@ -654,43 +654,43 @@
         <v>101325</v>
       </c>
       <c r="C5" t="n">
-        <v>6.275249102236224e+28</v>
+        <v>1.903015544154588e+30</v>
       </c>
       <c r="D5" t="n">
-        <v>1.908932684709977e+23</v>
+        <v>1.903015544154588e+30</v>
       </c>
       <c r="E5" t="n">
-        <v>20.78616204966218</v>
+        <v>12.4716972</v>
       </c>
       <c r="F5" t="n">
-        <v>29.10062684966218</v>
+        <v>20.786162</v>
       </c>
       <c r="G5" t="n">
-        <v>125.1667019412571</v>
+        <v>145.2212107224004</v>
       </c>
       <c r="H5" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>31601.2119344975</v>
+        <v>3117.9243</v>
       </c>
       <c r="J5" t="n">
-        <v>33679.8281344975</v>
+        <v>5196.540499999999</v>
       </c>
       <c r="K5" t="n">
-        <v>2388.15264918323</v>
+        <v>-31108.76218060011</v>
       </c>
       <c r="L5" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M5" t="n">
-        <v>-3045989.971668376</v>
+        <v>-3074473.259302873</v>
       </c>
       <c r="N5" t="n">
-        <v>-3043911.355468376</v>
+        <v>-3072394.643102873</v>
       </c>
       <c r="O5" t="n">
-        <v>-3075203.03095369</v>
+        <v>-3108699.945783474</v>
       </c>
     </row>
     <row r="6">
@@ -701,43 +701,43 @@
         <v>101325</v>
       </c>
       <c r="C6" t="n">
-        <v>1.187860201144289e+29</v>
+        <v>3.001894677551335e+30</v>
       </c>
       <c r="D6" t="n">
-        <v>3.001914842597709e+24</v>
+        <v>3.001894677551335e+30</v>
       </c>
       <c r="E6" t="n">
-        <v>20.78616438018154</v>
+        <v>12.4716972</v>
       </c>
       <c r="F6" t="n">
-        <v>29.10062918018154</v>
+        <v>20.786162</v>
       </c>
       <c r="G6" t="n">
-        <v>130.4723397556531</v>
+        <v>149.0109761380118</v>
       </c>
       <c r="H6" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>32640.52006773572</v>
+        <v>3741.50916</v>
       </c>
       <c r="J6" t="n">
-        <v>35134.85950773572</v>
+        <v>6235.848599999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-4006.842418960208</v>
+        <v>-38467.44424140353</v>
       </c>
       <c r="L6" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M6" t="n">
-        <v>-3044950.663535138</v>
+        <v>-3073849.674442873</v>
       </c>
       <c r="N6" t="n">
-        <v>-3042456.324095137</v>
+        <v>-3071355.335002873</v>
       </c>
       <c r="O6" t="n">
-        <v>-3081598.026021834</v>
+        <v>-3116058.627844277</v>
       </c>
     </row>
     <row r="7">
@@ -748,43 +748,43 @@
         <v>101325</v>
       </c>
       <c r="C7" t="n">
-        <v>2.037413130964578e+29</v>
+        <v>4.413289580777332e+30</v>
       </c>
       <c r="D7" t="n">
-        <v>2.336032315879771e+25</v>
+        <v>4.413289580777332e+30</v>
       </c>
       <c r="E7" t="n">
-        <v>20.78619799564271</v>
+        <v>12.4716972</v>
       </c>
       <c r="F7" t="n">
-        <v>29.10066279564271</v>
+        <v>20.786162</v>
       </c>
       <c r="G7" t="n">
-        <v>134.9581798209399</v>
+        <v>152.2151771413113</v>
       </c>
       <c r="H7" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>33679.82882824926</v>
+        <v>4365.09402</v>
       </c>
       <c r="J7" t="n">
-        <v>36589.89150824925</v>
+        <v>7275.1567</v>
       </c>
       <c r="K7" t="n">
-        <v>-10645.47142907971</v>
+        <v>-46000.15529945896</v>
       </c>
       <c r="L7" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M7" t="n">
-        <v>-3043911.354774624</v>
+        <v>-3073226.089582873</v>
       </c>
       <c r="N7" t="n">
-        <v>-3041001.292094624</v>
+        <v>-3070316.026902873</v>
       </c>
       <c r="O7" t="n">
-        <v>-3088236.655031953</v>
+        <v>-3123591.338902332</v>
       </c>
     </row>
     <row r="8">
@@ -795,43 +795,43 @@
         <v>101325</v>
       </c>
       <c r="C8" t="n">
-        <v>3.251254488081128e+29</v>
+        <v>6.162292267246822e+30</v>
       </c>
       <c r="D8" t="n">
-        <v>1.158846042726084e+26</v>
+        <v>6.162292267246822e+30</v>
       </c>
       <c r="E8" t="n">
-        <v>20.78642832761561</v>
+        <v>12.4716972</v>
       </c>
       <c r="F8" t="n">
-        <v>29.10089312761561</v>
+        <v>20.786162</v>
       </c>
       <c r="G8" t="n">
-        <v>138.8439927927024</v>
+        <v>154.9907823004902</v>
       </c>
       <c r="H8" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>34719.14294304322</v>
+        <v>4988.678879999999</v>
       </c>
       <c r="J8" t="n">
-        <v>38044.92886304321</v>
+        <v>8314.4648</v>
       </c>
       <c r="K8" t="n">
-        <v>-17492.66825403775</v>
+        <v>-53681.84812019607</v>
       </c>
       <c r="L8" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M8" t="n">
-        <v>-3042872.04065983</v>
+        <v>-3072602.504722873</v>
       </c>
       <c r="N8" t="n">
-        <v>-3039546.25473983</v>
+        <v>-3069276.718802873</v>
       </c>
       <c r="O8" t="n">
-        <v>-3095083.851856911</v>
+        <v>-3131273.031723069</v>
       </c>
     </row>
     <row r="9">
@@ -842,43 +842,43 @@
         <v>101325</v>
       </c>
       <c r="C9" t="n">
-        <v>4.910040339539897e+29</v>
+        <v>8.27224899927459e+30</v>
       </c>
       <c r="D9" t="n">
-        <v>4.228377480135973e+26</v>
+        <v>8.27224899927459e+30</v>
       </c>
       <c r="E9" t="n">
-        <v>20.78739039917788</v>
+        <v>12.4716972</v>
       </c>
       <c r="F9" t="n">
-        <v>29.10185519917788</v>
+        <v>20.786162</v>
       </c>
       <c r="G9" t="n">
-        <v>142.2715765962382</v>
+        <v>157.4390395604956</v>
       </c>
       <c r="H9" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>35758.48349810539</v>
+        <v>5612.263739999999</v>
       </c>
       <c r="J9" t="n">
-        <v>39499.9926581054</v>
+        <v>9353.7729</v>
       </c>
       <c r="K9" t="n">
-        <v>-24522.21681020182</v>
+        <v>-61493.79490222302</v>
       </c>
       <c r="L9" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M9" t="n">
-        <v>-3041832.700104768</v>
+        <v>-3071978.919862873</v>
       </c>
       <c r="N9" t="n">
-        <v>-3038091.190944768</v>
+        <v>-3068237.410702873</v>
       </c>
       <c r="O9" t="n">
-        <v>-3102113.400413075</v>
+        <v>-3139084.978505096</v>
       </c>
     </row>
     <row r="10">
@@ -889,43 +889,43 @@
         <v>101325</v>
       </c>
       <c r="C10" t="n">
-        <v>7.099655507229583e+29</v>
+        <v>1.076508156780094e+31</v>
       </c>
       <c r="D10" t="n">
-        <v>1.238274980591121e+27</v>
+        <v>1.076508156780094e+31</v>
       </c>
       <c r="E10" t="n">
-        <v>20.79024339657687</v>
+        <v>12.4716972</v>
       </c>
       <c r="F10" t="n">
-        <v>29.10470819657687</v>
+        <v>20.786162</v>
       </c>
       <c r="G10" t="n">
-        <v>145.3378408640347</v>
+        <v>159.6290803073627</v>
       </c>
       <c r="H10" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>36797.91308054789</v>
+        <v>6235.848599999999</v>
       </c>
       <c r="J10" t="n">
-        <v>40955.1454805479</v>
+        <v>10393.081</v>
       </c>
       <c r="K10" t="n">
-        <v>-31713.77495146944</v>
+        <v>-69421.45915368135</v>
       </c>
       <c r="L10" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M10" t="n">
-        <v>-3040793.270522325</v>
+        <v>-3071355.335002873</v>
       </c>
       <c r="N10" t="n">
-        <v>-3036636.038122325</v>
+        <v>-3067198.102602873</v>
       </c>
       <c r="O10" t="n">
-        <v>-3109304.958554343</v>
+        <v>-3147012.642756555</v>
       </c>
     </row>
     <row r="11">
@@ -936,43 +936,43 @@
         <v>101325</v>
       </c>
       <c r="C11" t="n">
-        <v>9.91093312396609e+29</v>
+        <v>1.366152048749547e+31</v>
       </c>
       <c r="D11" t="n">
-        <v>3.079355562487634e+27</v>
+        <v>1.366152048749547e+31</v>
       </c>
       <c r="E11" t="n">
-        <v>20.79686634529474</v>
+        <v>12.4716972</v>
       </c>
       <c r="F11" t="n">
-        <v>29.11133114529474</v>
+        <v>20.786162</v>
       </c>
       <c r="G11" t="n">
-        <v>148.1120566586225</v>
+        <v>161.6102131450245</v>
       </c>
       <c r="H11" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>37837.57034029537</v>
+        <v>6859.433459999999</v>
       </c>
       <c r="J11" t="n">
-        <v>42410.52598029537</v>
+        <v>11432.3891</v>
       </c>
       <c r="K11" t="n">
-        <v>-39051.10518194702</v>
+        <v>-77453.22812976351</v>
       </c>
       <c r="L11" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M11" t="n">
-        <v>-3039753.613262578</v>
+        <v>-3070731.750142873</v>
       </c>
       <c r="N11" t="n">
-        <v>-3035180.657622578</v>
+        <v>-3066158.794502873</v>
       </c>
       <c r="O11" t="n">
-        <v>-3116642.28878482</v>
+        <v>-3155044.411732637</v>
       </c>
     </row>
     <row r="12">
@@ -983,43 +983,43 @@
         <v>101325</v>
       </c>
       <c r="C12" t="n">
-        <v>1.343944368118657e+30</v>
+        <v>1.698128066323483e+31</v>
       </c>
       <c r="D12" t="n">
-        <v>6.75612708074956e+27</v>
+        <v>1.698128066323483e+31</v>
       </c>
       <c r="E12" t="n">
-        <v>20.80970918550415</v>
+        <v>12.4716972</v>
       </c>
       <c r="F12" t="n">
-        <v>29.12417398550415</v>
+        <v>20.786162</v>
       </c>
       <c r="G12" t="n">
-        <v>150.6455665881196</v>
+        <v>163.418845722974</v>
       </c>
       <c r="H12" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>38877.70324415049</v>
+        <v>7483.01832</v>
       </c>
       <c r="J12" t="n">
-        <v>43866.38212415048</v>
+        <v>12471.6972</v>
       </c>
       <c r="K12" t="n">
-        <v>-46520.95782872129</v>
+        <v>-85579.61023378442</v>
       </c>
       <c r="L12" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M12" t="n">
-        <v>-3038713.480358723</v>
+        <v>-3070108.165282873</v>
       </c>
       <c r="N12" t="n">
-        <v>-3033724.801478723</v>
+        <v>-3065119.486402873</v>
       </c>
       <c r="O12" t="n">
-        <v>-3124112.141431595</v>
+        <v>-3163170.793836658</v>
       </c>
     </row>
     <row r="13">
@@ -1030,43 +1030,43 @@
         <v>101325</v>
       </c>
       <c r="C13" t="n">
-        <v>1.778535206424751e+30</v>
+        <v>2.074319765522241e+31</v>
       </c>
       <c r="D13" t="n">
-        <v>1.343385916631244e+28</v>
+        <v>2.074319765522241e+31</v>
       </c>
       <c r="E13" t="n">
-        <v>20.83146072842154</v>
+        <v>12.4716972</v>
       </c>
       <c r="F13" t="n">
-        <v>29.14592552842154</v>
+        <v>20.786162</v>
       </c>
       <c r="G13" t="n">
-        <v>152.9775748407035</v>
+        <v>165.0826264115948</v>
       </c>
       <c r="H13" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>39918.68982215045</v>
+        <v>8106.60318</v>
       </c>
       <c r="J13" t="n">
-        <v>45323.09194215044</v>
+        <v>13511.0053</v>
       </c>
       <c r="K13" t="n">
-        <v>-54112.33170430683</v>
+        <v>-93792.70186753661</v>
       </c>
       <c r="L13" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M13" t="n">
-        <v>-3037672.493780723</v>
+        <v>-3069484.580422873</v>
       </c>
       <c r="N13" t="n">
-        <v>-3032268.091660723</v>
+        <v>-3064080.178302873</v>
       </c>
       <c r="O13" t="n">
-        <v>-3131703.51530718</v>
+        <v>-3171383.88547041</v>
       </c>
     </row>
     <row r="14">
@@ -1077,43 +1077,43 @@
         <v>101325</v>
       </c>
       <c r="C14" t="n">
-        <v>2.30533411746037e+30</v>
+        <v>2.496533591926069e+31</v>
       </c>
       <c r="D14" t="n">
-        <v>2.468503517309792e+28</v>
+        <v>2.496533591926069e+31</v>
       </c>
       <c r="E14" t="n">
-        <v>20.86466563731172</v>
+        <v>12.4716972</v>
       </c>
       <c r="F14" t="n">
-        <v>29.17913043731172</v>
+        <v>20.786162</v>
       </c>
       <c r="G14" t="n">
-        <v>155.1387578912737</v>
+        <v>166.6230467262736</v>
       </c>
       <c r="H14" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>40961.04047265605</v>
+        <v>8730.188039999999</v>
       </c>
       <c r="J14" t="n">
-        <v>46781.16583265606</v>
+        <v>14550.3134</v>
       </c>
       <c r="K14" t="n">
-        <v>-61815.96469123554</v>
+        <v>-102085.8193083915</v>
       </c>
       <c r="L14" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M14" t="n">
-        <v>-3036630.143130217</v>
+        <v>-3068860.995562873</v>
       </c>
       <c r="N14" t="n">
-        <v>-3030810.017770217</v>
+        <v>-3063040.870202873</v>
       </c>
       <c r="O14" t="n">
-        <v>-3139407.148294109</v>
+        <v>-3179677.002911265</v>
       </c>
     </row>
     <row r="15">
@@ -1124,43 +1124,43 @@
         <v>101325</v>
       </c>
       <c r="C15" t="n">
-        <v>2.935259818673294e+30</v>
+        <v>2.966507649062172e+31</v>
       </c>
       <c r="D15" t="n">
-        <v>4.253042906281482e+28</v>
+        <v>2.966507649062172e+31</v>
       </c>
       <c r="E15" t="n">
-        <v>20.91140480806995</v>
+        <v>12.4716972</v>
       </c>
       <c r="F15" t="n">
-        <v>29.22586960806995</v>
+        <v>20.786162</v>
       </c>
       <c r="G15" t="n">
-        <v>157.1536015390548</v>
+        <v>168.0571437298465</v>
       </c>
       <c r="H15" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>42005.38233341414</v>
+        <v>9353.7729</v>
       </c>
       <c r="J15" t="n">
-        <v>48241.23093341414</v>
+        <v>15589.6215</v>
       </c>
       <c r="K15" t="n">
-        <v>-69623.970220877</v>
+        <v>-110453.2362973849</v>
       </c>
       <c r="L15" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M15" t="n">
-        <v>-3035585.801269459</v>
+        <v>-3068237.410702873</v>
       </c>
       <c r="N15" t="n">
-        <v>-3029349.952669459</v>
+        <v>-3062001.562102873</v>
       </c>
       <c r="O15" t="n">
-        <v>-3147215.15382375</v>
+        <v>-3188044.419900258</v>
       </c>
     </row>
     <row r="16">
@@ -1171,43 +1171,43 @@
         <v>101325</v>
       </c>
       <c r="C16" t="n">
-        <v>3.679685638048841e+30</v>
+        <v>3.485918919858922e+31</v>
       </c>
       <c r="D16" t="n">
-        <v>6.947012917212696e+28</v>
+        <v>3.485918919858922e+31</v>
       </c>
       <c r="E16" t="n">
-        <v>20.97309714907115</v>
+        <v>12.4716972</v>
       </c>
       <c r="F16" t="n">
-        <v>29.28756194907115</v>
+        <v>20.786162</v>
       </c>
       <c r="G16" t="n">
-        <v>159.0419650914217</v>
+        <v>169.3986518854525</v>
       </c>
       <c r="H16" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>43052.43058697424</v>
+        <v>9977.357759999999</v>
       </c>
       <c r="J16" t="n">
-        <v>49704.00242697424</v>
+        <v>16628.9296</v>
       </c>
       <c r="K16" t="n">
-        <v>-77529.56964616315</v>
+        <v>-118889.991908362</v>
       </c>
       <c r="L16" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M16" t="n">
-        <v>-3034538.753015899</v>
+        <v>-3067613.825842873</v>
       </c>
       <c r="N16" t="n">
-        <v>-3027887.181175899</v>
+        <v>-3060962.254002873</v>
       </c>
       <c r="O16" t="n">
-        <v>-3155120.753249036</v>
+        <v>-3196481.175511235</v>
       </c>
     </row>
     <row r="17">
@@ -1218,43 +1218,43 @@
         <v>101325</v>
       </c>
       <c r="C17" t="n">
-        <v>4.550448315266735e+30</v>
+        <v>4.05638929851281e+31</v>
       </c>
       <c r="D17" t="n">
-        <v>1.085060817893397e+29</v>
+        <v>4.05638929851281e+31</v>
       </c>
       <c r="E17" t="n">
-        <v>21.05042871712589</v>
+        <v>12.4716972</v>
       </c>
       <c r="F17" t="n">
-        <v>29.36489351712589</v>
+        <v>20.786162</v>
       </c>
       <c r="G17" t="n">
-        <v>160.8201622485371</v>
+        <v>170.6588050957176</v>
       </c>
       <c r="H17" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>44102.95309609771</v>
+        <v>10600.94262</v>
       </c>
       <c r="J17" t="n">
-        <v>51170.24817609772</v>
+        <v>17668.2377</v>
       </c>
       <c r="K17" t="n">
-        <v>-85526.88973515877</v>
+        <v>-127391.74663136</v>
       </c>
       <c r="L17" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M17" t="n">
-        <v>-3033488.230506775</v>
+        <v>-3066990.240982873</v>
       </c>
       <c r="N17" t="n">
-        <v>-3026420.935426775</v>
+        <v>-3059922.945902873</v>
       </c>
       <c r="O17" t="n">
-        <v>-3163118.073338032</v>
+        <v>-3204982.930234233</v>
       </c>
     </row>
     <row r="18">
@@ -1265,43 +1265,43 @@
         <v>101325</v>
       </c>
       <c r="C18" t="n">
-        <v>5.559860375004448e+30</v>
+        <v>4.679490690440556e+31</v>
       </c>
       <c r="D18" t="n">
-        <v>1.631579465328065e+29</v>
+        <v>4.679490690440556e+31</v>
       </c>
       <c r="E18" t="n">
-        <v>21.1433842612987</v>
+        <v>12.4716972</v>
       </c>
       <c r="F18" t="n">
-        <v>29.4578490612987</v>
+        <v>20.786162</v>
       </c>
       <c r="G18" t="n">
-        <v>162.5017314634849</v>
+        <v>171.8469091454579</v>
       </c>
       <c r="H18" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>45157.73419542756</v>
+        <v>11224.52748</v>
       </c>
       <c r="J18" t="n">
-        <v>52640.75251542756</v>
+        <v>18707.5458</v>
       </c>
       <c r="K18" t="n">
-        <v>-93610.80580170883</v>
+        <v>-135954.6724309121</v>
       </c>
       <c r="L18" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M18" t="n">
-        <v>-3032433.449407446</v>
+        <v>-3066366.656122873</v>
       </c>
       <c r="N18" t="n">
-        <v>-3024950.431087445</v>
+        <v>-3058883.637802873</v>
       </c>
       <c r="O18" t="n">
-        <v>-3171201.989404582</v>
+        <v>-3213545.856033785</v>
       </c>
     </row>
     <row r="19">
@@ -1312,43 +1312,43 @@
         <v>101325</v>
       </c>
       <c r="C19" t="n">
-        <v>6.720725041640927e+30</v>
+        <v>5.356749370343734e+31</v>
       </c>
       <c r="D19" t="n">
-        <v>2.374739817449764e+29</v>
+        <v>5.356749370343734e+31</v>
       </c>
       <c r="E19" t="n">
-        <v>21.25134545451133</v>
+        <v>12.4716972</v>
       </c>
       <c r="F19" t="n">
-        <v>29.56581025451133</v>
+        <v>20.786162</v>
       </c>
       <c r="G19" t="n">
-        <v>164.098001305994</v>
+        <v>172.9707591656717</v>
       </c>
       <c r="H19" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>46217.54187888293</v>
+        <v>11848.11234</v>
       </c>
       <c r="J19" t="n">
-        <v>54116.28343888294</v>
+        <v>19746.8539</v>
       </c>
       <c r="K19" t="n">
-        <v>-101776.8178018114</v>
+        <v>-144575.3673073881</v>
       </c>
       <c r="L19" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M19" t="n">
-        <v>-3031373.64172399</v>
+        <v>-3065743.071262873</v>
       </c>
       <c r="N19" t="n">
-        <v>-3023474.90016399</v>
+        <v>-3057844.329702873</v>
       </c>
       <c r="O19" t="n">
-        <v>-3179368.001404685</v>
+        <v>-3222166.550910261</v>
       </c>
     </row>
     <row r="20">
@@ -1359,43 +1359,43 @@
         <v>101325</v>
       </c>
       <c r="C20" t="n">
-        <v>8.046352767372724e+30</v>
+        <v>6.089649741294682e+31</v>
       </c>
       <c r="D20" t="n">
-        <v>3.360384554605005e+29</v>
+        <v>6.089649741294682e+31</v>
       </c>
       <c r="E20" t="n">
-        <v>21.37322214641092</v>
+        <v>12.4716972</v>
       </c>
       <c r="F20" t="n">
-        <v>29.68768694641092</v>
+        <v>20.786162</v>
       </c>
       <c r="G20" t="n">
-        <v>165.6185165739516</v>
+        <v>174.036949892325</v>
       </c>
       <c r="H20" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>47283.10085034958</v>
+        <v>12471.6972</v>
       </c>
       <c r="J20" t="n">
-        <v>55597.56565034958</v>
+        <v>20786.162</v>
       </c>
       <c r="K20" t="n">
-        <v>-110020.950923602</v>
+        <v>-153250.787892325</v>
       </c>
       <c r="L20" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M20" t="n">
-        <v>-3030308.082752523</v>
+        <v>-3065119.486402873</v>
       </c>
       <c r="N20" t="n">
-        <v>-3021993.617952524</v>
+        <v>-3056805.021602873</v>
       </c>
       <c r="O20" t="n">
-        <v>-3187612.134526475</v>
+        <v>-3230841.971495198</v>
       </c>
     </row>
     <row r="21">
@@ -1406,43 +1406,43 @@
         <v>101325</v>
       </c>
       <c r="C21" t="n">
-        <v>9.550578597339795e+30</v>
+        <v>6.879637604178619e+31</v>
       </c>
       <c r="D21" t="n">
-        <v>4.639767995280916e+29</v>
+        <v>6.879637604178619e+31</v>
       </c>
       <c r="E21" t="n">
-        <v>21.50759080189067</v>
+        <v>12.4716972</v>
       </c>
       <c r="F21" t="n">
-        <v>29.82205560189067</v>
+        <v>20.786162</v>
       </c>
       <c r="G21" t="n">
-        <v>167.0713669366133</v>
+        <v>175.0511101487573</v>
       </c>
       <c r="H21" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>48355.07240530431</v>
+        <v>13095.28206</v>
       </c>
       <c r="J21" t="n">
-        <v>57085.26044530432</v>
+        <v>21825.4701</v>
       </c>
       <c r="K21" t="n">
-        <v>-118339.6748381396</v>
+        <v>-161978.1955561952</v>
       </c>
       <c r="L21" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M21" t="n">
-        <v>-3029236.111197569</v>
+        <v>-3064495.901542873</v>
       </c>
       <c r="N21" t="n">
-        <v>-3020505.923157569</v>
+        <v>-3055765.713502873</v>
       </c>
       <c r="O21" t="n">
-        <v>-3195930.858441013</v>
+        <v>-3239569.379159069</v>
       </c>
     </row>
     <row r="22">
@@ -1453,43 +1453,43 @@
         <v>101325</v>
       </c>
       <c r="C22" t="n">
-        <v>1.124777976294719e+31</v>
+        <v>7.728123022421593e+31</v>
       </c>
       <c r="D22" t="n">
-        <v>6.269594465246391e+29</v>
+        <v>7.728123022421593e+31</v>
       </c>
       <c r="E22" t="n">
-        <v>21.65282323840096</v>
+        <v>12.4716972</v>
       </c>
       <c r="F22" t="n">
-        <v>29.96728803840096</v>
+        <v>20.786162</v>
       </c>
       <c r="G22" t="n">
-        <v>168.463445269638</v>
+        <v>176.0180827299868</v>
       </c>
       <c r="H22" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>49434.04104469834</v>
+        <v>13718.86692</v>
       </c>
       <c r="J22" t="n">
-        <v>58579.95232469834</v>
+        <v>22864.7782</v>
       </c>
       <c r="K22" t="n">
-        <v>-126729.8374719034</v>
+        <v>-170755.1128029855</v>
       </c>
       <c r="L22" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M22" t="n">
-        <v>-3028157.142558175</v>
+        <v>-3063872.316682873</v>
       </c>
       <c r="N22" t="n">
-        <v>-3019011.231278175</v>
+        <v>-3054726.405402873</v>
       </c>
       <c r="O22" t="n">
-        <v>-3204321.021074777</v>
+        <v>-3248346.296405859</v>
       </c>
     </row>
     <row r="23">
@@ -1500,43 +1500,43 @@
         <v>101325</v>
       </c>
       <c r="C23" t="n">
-        <v>1.315289305536852e+31</v>
+        <v>8.636482848876366e+31</v>
       </c>
       <c r="D23" t="n">
-        <v>8.312050402172344e+29</v>
+        <v>8.636482848876366e+31</v>
       </c>
       <c r="E23" t="n">
-        <v>21.80719648775018</v>
+        <v>12.4716972</v>
       </c>
       <c r="F23" t="n">
-        <v>30.12166128775017</v>
+        <v>20.786162</v>
       </c>
       <c r="G23" t="n">
-        <v>169.8006538033105</v>
+        <v>176.9420642679697</v>
       </c>
       <c r="H23" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>50520.50707859044</v>
+        <v>14342.45178</v>
       </c>
       <c r="J23" t="n">
-        <v>60082.14159859045</v>
+        <v>23904.0863</v>
       </c>
       <c r="K23" t="n">
-        <v>-135188.6102752167</v>
+        <v>-179579.2876081651</v>
       </c>
       <c r="L23" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M23" t="n">
-        <v>-3027070.676524283</v>
+        <v>-3063248.731822873</v>
       </c>
       <c r="N23" t="n">
-        <v>-3017509.042004283</v>
+        <v>-3053687.097302873</v>
       </c>
       <c r="O23" t="n">
-        <v>-3212779.79387809</v>
+        <v>-3257170.471211039</v>
       </c>
     </row>
     <row r="24">
@@ -1547,43 +1547,43 @@
         <v>101325</v>
       </c>
       <c r="C24" t="n">
-        <v>1.528143167212045e+31</v>
+        <v>9.606062968164273e+31</v>
       </c>
       <c r="D24" t="n">
-        <v>1.083483502601505e+30</v>
+        <v>9.606062968164273e+31</v>
       </c>
       <c r="E24" t="n">
-        <v>21.9689802871986</v>
+        <v>12.4716972</v>
       </c>
       <c r="F24" t="n">
-        <v>30.2834450871986</v>
+        <v>20.786162</v>
       </c>
       <c r="G24" t="n">
-        <v>171.0880705351632</v>
+        <v>177.8267153079363</v>
       </c>
       <c r="H24" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>51614.88416908446</v>
+        <v>14966.03664</v>
       </c>
       <c r="J24" t="n">
-        <v>61592.24192908446</v>
+        <v>24943.3944</v>
       </c>
       <c r="K24" t="n">
-        <v>-143713.4427131113</v>
+        <v>-188448.6639695236</v>
       </c>
       <c r="L24" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M24" t="n">
-        <v>-3025976.299433789</v>
+        <v>-3062625.146962873</v>
       </c>
       <c r="N24" t="n">
-        <v>-3015998.941673789</v>
+        <v>-3052647.789202873</v>
       </c>
       <c r="O24" t="n">
-        <v>-3221304.626315984</v>
+        <v>-3266039.847572397</v>
       </c>
     </row>
     <row r="25">
@@ -1594,43 +1594,43 @@
         <v>101325</v>
       </c>
       <c r="C25" t="n">
-        <v>1.764950134502542e+31</v>
+        <v>1.063818029742103e+32</v>
       </c>
       <c r="D25" t="n">
-        <v>1.391119275976541e+30</v>
+        <v>1.063818029742103e+32</v>
       </c>
       <c r="E25" t="n">
-        <v>22.13650239172824</v>
+        <v>12.4716972</v>
       </c>
       <c r="F25" t="n">
-        <v>30.45096719172824</v>
+        <v>20.786162</v>
       </c>
       <c r="G25" t="n">
-        <v>172.330084733113</v>
+        <v>178.6752478991975</v>
       </c>
       <c r="H25" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>52717.50068716373</v>
+        <v>15589.6215</v>
       </c>
       <c r="J25" t="n">
-        <v>63110.58168716373</v>
+        <v>25982.7025</v>
       </c>
       <c r="K25" t="n">
-        <v>-152302.0242292275</v>
+        <v>-197361.3573739968</v>
       </c>
       <c r="L25" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M25" t="n">
-        <v>-3024873.682915709</v>
+        <v>-3062001.562102873</v>
       </c>
       <c r="N25" t="n">
-        <v>-3014480.60191571</v>
+        <v>-3051608.481102873</v>
       </c>
       <c r="O25" t="n">
-        <v>-3229893.207832101</v>
+        <v>-3274952.54097687</v>
       </c>
     </row>
     <row r="26">
@@ -1641,43 +1641,43 @@
         <v>101325</v>
       </c>
       <c r="C26" t="n">
-        <v>2.02738156472954e+31</v>
+        <v>1.173412458040053e+32</v>
       </c>
       <c r="D26" t="n">
-        <v>1.761994933673399e+30</v>
+        <v>1.173412458040053e+32</v>
       </c>
       <c r="E26" t="n">
-        <v>22.30819398360381</v>
+        <v>12.4716972</v>
       </c>
       <c r="F26" t="n">
-        <v>30.6226587836038</v>
+        <v>20.786162</v>
       </c>
       <c r="G26" t="n">
-        <v>173.5305079811429</v>
+        <v>179.4904959965571</v>
       </c>
       <c r="H26" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>53828.60382542046</v>
+        <v>16213.20636</v>
       </c>
       <c r="J26" t="n">
-        <v>64637.40806542046</v>
+        <v>27022.0106</v>
       </c>
       <c r="K26" t="n">
-        <v>-160952.2523100653</v>
+        <v>-206315.6341955242</v>
       </c>
       <c r="L26" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M26" t="n">
-        <v>-3023762.579777453</v>
+        <v>-3061377.977242873</v>
       </c>
       <c r="N26" t="n">
-        <v>-3012953.775537453</v>
+        <v>-3050569.173002873</v>
       </c>
       <c r="O26" t="n">
-        <v>-3238543.435912938</v>
+        <v>-3283906.817798398</v>
       </c>
     </row>
     <row r="27">
@@ -1688,43 +1688,43 @@
         <v>101325</v>
       </c>
       <c r="C27" t="n">
-        <v>2.317171044324043e+31</v>
+        <v>1.289516000364395e+32</v>
       </c>
       <c r="D27" t="n">
-        <v>2.204555262058526e+30</v>
+        <v>1.289516000364395e+32</v>
       </c>
       <c r="E27" t="n">
-        <v>22.48261839821689</v>
+        <v>12.4716972</v>
       </c>
       <c r="F27" t="n">
-        <v>30.79708319821689</v>
+        <v>20.786162</v>
       </c>
       <c r="G27" t="n">
-        <v>174.6926656191789</v>
+        <v>180.2749725679417</v>
       </c>
       <c r="H27" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>54948.3655498974</v>
+        <v>16836.79122</v>
       </c>
       <c r="J27" t="n">
-        <v>66172.8930298974</v>
+        <v>28061.3187</v>
       </c>
       <c r="K27" t="n">
-        <v>-169662.2055559941</v>
+        <v>-215309.8942667213</v>
       </c>
       <c r="L27" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M27" t="n">
-        <v>-3022642.818052976</v>
+        <v>-3060754.392382873</v>
       </c>
       <c r="N27" t="n">
-        <v>-3011418.290572976</v>
+        <v>-3049529.864902873</v>
       </c>
       <c r="O27" t="n">
-        <v>-3247253.389158867</v>
+        <v>-3292901.077869595</v>
       </c>
     </row>
     <row r="28">
@@ -1735,43 +1735,43 @@
         <v>101325</v>
       </c>
       <c r="C28" t="n">
-        <v>2.636115748994653e+31</v>
+        <v>1.412252665848746e+32</v>
       </c>
       <c r="D28" t="n">
-        <v>2.727811852767945e+30</v>
+        <v>1.412252665848746e+32</v>
       </c>
       <c r="E28" t="n">
-        <v>22.65848659355306</v>
+        <v>12.4716972</v>
       </c>
       <c r="F28" t="n">
-        <v>30.97295139355306</v>
+        <v>20.786162</v>
       </c>
       <c r="G28" t="n">
-        <v>175.8194723146703</v>
+        <v>181.0309163112358</v>
       </c>
       <c r="H28" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>56076.88964275298</v>
+        <v>17460.37608</v>
       </c>
       <c r="J28" t="n">
-        <v>67717.14036275298</v>
+        <v>29100.6268</v>
       </c>
       <c r="K28" t="n">
-        <v>-178430.1208777854</v>
+        <v>-224342.6560357302</v>
       </c>
       <c r="L28" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M28" t="n">
-        <v>-3021514.29396012</v>
+        <v>-3060130.807522873</v>
       </c>
       <c r="N28" t="n">
-        <v>-3009874.04324012</v>
+        <v>-3048490.556802873</v>
       </c>
       <c r="O28" t="n">
-        <v>-3256021.304480659</v>
+        <v>-3301933.839638603</v>
       </c>
     </row>
     <row r="29">
@@ -1782,43 +1782,43 @@
         <v>101325</v>
       </c>
       <c r="C29" t="n">
-        <v>2.986077723022494e+31</v>
+        <v>1.541744186874665e+32</v>
       </c>
       <c r="D29" t="n">
-        <v>3.341348201624478e+30</v>
+        <v>1.541744186874665e+32</v>
       </c>
       <c r="E29" t="n">
-        <v>22.83466257522961</v>
+        <v>12.4716972</v>
       </c>
       <c r="F29" t="n">
-        <v>31.14912737522961</v>
+        <v>20.786162</v>
       </c>
       <c r="G29" t="n">
-        <v>176.9134947016536</v>
+        <v>181.7603301696267</v>
       </c>
       <c r="H29" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>57214.21925469265</v>
+        <v>18083.96094</v>
       </c>
       <c r="J29" t="n">
-        <v>69270.19321469264</v>
+        <v>30139.9349</v>
       </c>
       <c r="K29" t="n">
-        <v>-187254.374102705</v>
+        <v>-233412.5438459588</v>
       </c>
       <c r="L29" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M29" t="n">
-        <v>-3020376.964348181</v>
+        <v>-3059507.222662873</v>
       </c>
       <c r="N29" t="n">
-        <v>-3008320.990388181</v>
+        <v>-3047451.248702873</v>
       </c>
       <c r="O29" t="n">
-        <v>-3264845.557705578</v>
+        <v>-3311003.727448832</v>
       </c>
     </row>
     <row r="30">
@@ -1829,43 +1829,43 @@
         <v>101325</v>
       </c>
       <c r="C30" t="n">
-        <v>3.368985083400595e+31</v>
+        <v>1.6781101400749e+32</v>
       </c>
       <c r="D30" t="n">
-        <v>4.055325283996614e+30</v>
+        <v>1.6781101400749e+32</v>
       </c>
       <c r="E30" t="n">
-        <v>23.01016156542347</v>
+        <v>12.4716972</v>
       </c>
       <c r="F30" t="n">
-        <v>31.32462636542347</v>
+        <v>20.786162</v>
       </c>
       <c r="G30" t="n">
-        <v>177.9770034278299</v>
+        <v>182.4650133148088</v>
       </c>
       <c r="H30" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>58360.34453664527</v>
+        <v>18707.5458</v>
       </c>
       <c r="J30" t="n">
-        <v>70832.04173664527</v>
+        <v>31179.243</v>
       </c>
       <c r="K30" t="n">
-        <v>-196133.4634050996</v>
+        <v>-242518.2769722132</v>
       </c>
       <c r="L30" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M30" t="n">
-        <v>-3019230.839066228</v>
+        <v>-3058883.637802873</v>
       </c>
       <c r="N30" t="n">
-        <v>-3006759.141866228</v>
+        <v>-3046411.940602873</v>
       </c>
       <c r="O30" t="n">
-        <v>-3273724.647007973</v>
+        <v>-3320109.460575087</v>
       </c>
     </row>
     <row r="31">
@@ -1876,43 +1876,43 @@
         <v>101325</v>
       </c>
       <c r="C31" t="n">
-        <v>3.786833155440942e+31</v>
+        <v>1.821468056981535e+32</v>
       </c>
       <c r="D31" t="n">
-        <v>4.880487561087579e+30</v>
+        <v>1.821468056981535e+32</v>
       </c>
       <c r="E31" t="n">
-        <v>23.1841432096721</v>
+        <v>12.4716972</v>
       </c>
       <c r="F31" t="n">
-        <v>31.4986080096721</v>
+        <v>20.786162</v>
       </c>
       <c r="G31" t="n">
-        <v>179.0120164960102</v>
+        <v>183.1465878839588</v>
       </c>
       <c r="H31" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>59515.21004731249</v>
+        <v>19331.13066</v>
       </c>
       <c r="J31" t="n">
-        <v>72402.63048731249</v>
+        <v>32218.5511</v>
       </c>
       <c r="K31" t="n">
-        <v>-205065.9950815034</v>
+        <v>-251658.6601201361</v>
       </c>
       <c r="L31" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M31" t="n">
-        <v>-3018075.973555561</v>
+        <v>-3058260.052942873</v>
       </c>
       <c r="N31" t="n">
-        <v>-3005188.553115561</v>
+        <v>-3045372.632502873</v>
       </c>
       <c r="O31" t="n">
-        <v>-3282657.178684377</v>
+        <v>-3329249.843723009</v>
       </c>
     </row>
     <row r="32">
@@ -1923,43 +1923,43 @@
         <v>101325</v>
       </c>
       <c r="C32" t="n">
-        <v>4.24168554676256e+31</v>
+        <v>1.971933525518983e+32</v>
       </c>
       <c r="D32" t="n">
-        <v>5.82816936435128e+30</v>
+        <v>1.971933525518983e+32</v>
       </c>
       <c r="E32" t="n">
-        <v>23.35590163074782</v>
+        <v>12.4716972</v>
       </c>
       <c r="F32" t="n">
-        <v>31.67036643074782</v>
+        <v>20.786162</v>
       </c>
       <c r="G32" t="n">
-        <v>180.020335431949</v>
+        <v>183.8065214704147</v>
       </c>
       <c r="H32" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>60678.72173564869</v>
+        <v>19954.71552</v>
       </c>
       <c r="J32" t="n">
-        <v>73981.8654156487</v>
+        <v>33257.8592</v>
       </c>
       <c r="K32" t="n">
-        <v>-214050.6712754696</v>
+        <v>-260832.5751526636</v>
       </c>
       <c r="L32" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M32" t="n">
-        <v>-3016912.461867224</v>
+        <v>-3057636.468082873</v>
       </c>
       <c r="N32" t="n">
-        <v>-3003609.318187225</v>
+        <v>-3044333.324402873</v>
       </c>
       <c r="O32" t="n">
-        <v>-3291641.854878343</v>
+        <v>-3338423.758755537</v>
       </c>
     </row>
     <row r="33">
@@ -1970,43 +1970,43 @@
         <v>101325</v>
       </c>
       <c r="C33" t="n">
-        <v>4.735675166454784e+31</v>
+        <v>2.129620283368675e+32</v>
       </c>
       <c r="D33" t="n">
-        <v>6.910301603301866e+30</v>
+        <v>2.129620283368675e+32</v>
       </c>
       <c r="E33" t="n">
-        <v>23.52485370496343</v>
+        <v>12.4716972</v>
       </c>
       <c r="F33" t="n">
-        <v>31.83931850496343</v>
+        <v>20.786162</v>
       </c>
       <c r="G33" t="n">
-        <v>181.0035755294275</v>
+        <v>184.4461461524706</v>
       </c>
       <c r="H33" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>61850.7533766819</v>
+        <v>20578.30038</v>
       </c>
       <c r="J33" t="n">
-        <v>75569.6202966819</v>
+        <v>34297.1673</v>
       </c>
       <c r="K33" t="n">
-        <v>-223086.2793268734</v>
+        <v>-270038.9738515764</v>
       </c>
       <c r="L33" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M33" t="n">
-        <v>-3015740.430226191</v>
+        <v>-3057012.883222873</v>
       </c>
       <c r="N33" t="n">
-        <v>-3002021.563306191</v>
+        <v>-3043294.016302873</v>
       </c>
       <c r="O33" t="n">
-        <v>-3300677.462929747</v>
+        <v>-3347630.15745445</v>
       </c>
     </row>
     <row r="34">
@@ -2017,43 +2017,43 @@
         <v>101325</v>
       </c>
       <c r="C34" t="n">
-        <v>5.271005195835574e+31</v>
+        <v>2.29464030408876e+32</v>
       </c>
       <c r="D34" t="n">
-        <v>8.139418743487993e+30</v>
+        <v>2.29464030408876e+32</v>
       </c>
       <c r="E34" t="n">
-        <v>23.69052657011891</v>
+        <v>12.4716972</v>
       </c>
       <c r="F34" t="n">
-        <v>32.00499137011891</v>
+        <v>20.786162</v>
       </c>
       <c r="G34" t="n">
-        <v>181.9631911975793</v>
+        <v>185.0666746806799</v>
       </c>
       <c r="H34" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>63031.15239840503</v>
+        <v>21201.88524</v>
       </c>
       <c r="J34" t="n">
-        <v>77165.74255840504</v>
+        <v>35336.4754</v>
       </c>
       <c r="K34" t="n">
-        <v>-232171.6824774797</v>
+        <v>-279276.8715571559</v>
       </c>
       <c r="L34" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M34" t="n">
-        <v>-3014560.031204468</v>
+        <v>-3056389.298362873</v>
       </c>
       <c r="N34" t="n">
-        <v>-3000425.441044468</v>
+        <v>-3042254.708202873</v>
       </c>
       <c r="O34" t="n">
-        <v>-3309762.866080353</v>
+        <v>-3356868.055160029</v>
       </c>
     </row>
     <row r="35">
@@ -2064,43 +2064,43 @@
         <v>101325</v>
       </c>
       <c r="C35" t="n">
-        <v>5.849950016706562e+31</v>
+        <v>2.467103876752415e+32</v>
       </c>
       <c r="D35" t="n">
-        <v>9.528666004959944e+30</v>
+        <v>2.467103876752415e+32</v>
       </c>
       <c r="E35" t="n">
-        <v>23.85254507812528</v>
+        <v>12.4716972</v>
       </c>
       <c r="F35" t="n">
-        <v>32.16700987812528</v>
+        <v>20.786162</v>
       </c>
       <c r="G35" t="n">
-        <v>182.9004972524501</v>
+        <v>185.6692143181083</v>
       </c>
       <c r="H35" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>64219.74508023942</v>
+        <v>21825.4701</v>
       </c>
       <c r="J35" t="n">
-        <v>78770.05848023942</v>
+        <v>36375.7835</v>
       </c>
       <c r="K35" t="n">
-        <v>-241305.8117115483</v>
+        <v>-288545.3415566896</v>
       </c>
       <c r="L35" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M35" t="n">
-        <v>-3013371.438522634</v>
+        <v>-3055765.713502873</v>
       </c>
       <c r="N35" t="n">
-        <v>-2998821.125122634</v>
+        <v>-3041215.400102873</v>
       </c>
       <c r="O35" t="n">
-        <v>-3318896.995314422</v>
+        <v>-3366136.525159563</v>
       </c>
     </row>
     <row r="36">
@@ -2111,43 +2111,43 @@
         <v>101325</v>
       </c>
       <c r="C36" t="n">
-        <v>6.474856102422154e+31</v>
+        <v>2.647119679767869e+32</v>
       </c>
       <c r="D36" t="n">
-        <v>1.109180673620582e+31</v>
+        <v>2.647119679767869e+32</v>
       </c>
       <c r="E36" t="n">
-        <v>24.01061967372003</v>
+        <v>12.4716972</v>
       </c>
       <c r="F36" t="n">
-        <v>32.32508447372003</v>
+        <v>20.786162</v>
       </c>
       <c r="G36" t="n">
-        <v>183.8166868456752</v>
+        <v>186.2547787304201</v>
       </c>
       <c r="H36" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>65416.341133181</v>
+        <v>22449.05496</v>
       </c>
       <c r="J36" t="n">
-        <v>80382.377773181</v>
+        <v>37415.0916</v>
       </c>
       <c r="K36" t="n">
-        <v>-250487.6585490344</v>
+        <v>-297843.5101147562</v>
       </c>
       <c r="L36" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M36" t="n">
-        <v>-3012174.842469692</v>
+        <v>-3055142.128642873</v>
       </c>
       <c r="N36" t="n">
-        <v>-2997208.805829692</v>
+        <v>-3040176.092002873</v>
       </c>
       <c r="O36" t="n">
-        <v>-3328078.842151908</v>
+        <v>-3375434.69371763</v>
       </c>
     </row>
     <row r="37">
@@ -2158,43 +2158,43 @@
         <v>101325</v>
       </c>
       <c r="C37" t="n">
-        <v>7.148142876491289e+31</v>
+        <v>2.834794849458501e+32</v>
       </c>
       <c r="D37" t="n">
-        <v>1.284322992362316e+31</v>
+        <v>2.834794849458501e+32</v>
       </c>
       <c r="E37" t="n">
-        <v>24.16453500476493</v>
+        <v>12.4716972</v>
       </c>
       <c r="F37" t="n">
-        <v>32.47899980476493</v>
+        <v>20.786162</v>
       </c>
       <c r="G37" t="n">
-        <v>184.7128466012161</v>
+        <v>186.8242982465281</v>
       </c>
       <c r="H37" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>66620.73769120139</v>
+        <v>23072.63982</v>
       </c>
       <c r="J37" t="n">
-        <v>82002.49757120138</v>
+        <v>38454.3997</v>
       </c>
       <c r="K37" t="n">
-        <v>-259716.2686410485</v>
+        <v>-307170.5520560769</v>
       </c>
       <c r="L37" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M37" t="n">
-        <v>-3010970.445911672</v>
+        <v>-3054518.543782873</v>
       </c>
       <c r="N37" t="n">
-        <v>-2995588.686031672</v>
+        <v>-3039136.783902873</v>
       </c>
       <c r="O37" t="n">
-        <v>-3337307.452243922</v>
+        <v>-3384761.73565895</v>
       </c>
     </row>
     <row r="38">
@@ -2205,43 +2205,43 @@
         <v>101325</v>
       </c>
       <c r="C38" t="n">
-        <v>7.872303542850857e+31</v>
+        <v>3.030235043909458e+32</v>
       </c>
       <c r="D38" t="n">
-        <v>1.479795780170488e+31</v>
+        <v>3.030235043909458e+32</v>
       </c>
       <c r="E38" t="n">
-        <v>24.31413943962245</v>
+        <v>12.4716972</v>
       </c>
       <c r="F38" t="n">
-        <v>32.62860423962245</v>
+        <v>20.786162</v>
       </c>
       <c r="G38" t="n">
-        <v>185.5899694311489</v>
+        <v>187.3786287506339</v>
       </c>
       <c r="H38" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>67832.72275532853</v>
+        <v>23696.22468</v>
       </c>
       <c r="J38" t="n">
-        <v>83630.20587532854</v>
+        <v>39493.7078</v>
       </c>
       <c r="K38" t="n">
-        <v>-268990.7360438545</v>
+        <v>-316525.6868262045</v>
       </c>
       <c r="L38" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M38" t="n">
-        <v>-3009758.460847544</v>
+        <v>-3053894.958922873</v>
       </c>
       <c r="N38" t="n">
-        <v>-2993960.977727544</v>
+        <v>-3038097.475802873</v>
       </c>
       <c r="O38" t="n">
-        <v>-3346581.919646728</v>
+        <v>-3394116.870429078</v>
       </c>
     </row>
     <row r="39">
@@ -2252,43 +2252,43 @@
         <v>101325</v>
       </c>
       <c r="C39" t="n">
-        <v>8.64990589140827e+31</v>
+        <v>3.233544502525993e+32</v>
       </c>
       <c r="D39" t="n">
-        <v>1.697165353399354e+31</v>
+        <v>3.233544502525993e+32</v>
       </c>
       <c r="E39" t="n">
-        <v>24.45933557372731</v>
+        <v>12.4716972</v>
       </c>
       <c r="F39" t="n">
-        <v>32.77380037372731</v>
+        <v>20.786162</v>
       </c>
       <c r="G39" t="n">
-        <v>186.4489654194574</v>
+        <v>187.9185594190409</v>
       </c>
       <c r="H39" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>69052.0781381384</v>
+        <v>24319.80954</v>
       </c>
       <c r="J39" t="n">
-        <v>85265.2844981384</v>
+        <v>40533.0159</v>
       </c>
       <c r="K39" t="n">
-        <v>-278310.1980698035</v>
+        <v>-325908.1749671297</v>
       </c>
       <c r="L39" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M39" t="n">
-        <v>-3008539.105464735</v>
+        <v>-3053271.374062873</v>
       </c>
       <c r="N39" t="n">
-        <v>-2992325.899104735</v>
+        <v>-3037058.167702873</v>
       </c>
       <c r="O39" t="n">
-        <v>-3355901.381672677</v>
+        <v>-3403499.358570003</v>
       </c>
     </row>
     <row r="40">
@@ -2299,43 +2299,43 @@
         <v>101325</v>
       </c>
       <c r="C40" t="n">
-        <v>9.483593081958351e+31</v>
+        <v>3.4448261016963e+32</v>
       </c>
       <c r="D40" t="n">
-        <v>1.938062893935238e+31</v>
+        <v>3.4448261016963e+32</v>
       </c>
       <c r="E40" t="n">
-        <v>24.60007174249671</v>
+        <v>12.4716972</v>
       </c>
       <c r="F40" t="n">
-        <v>32.91453654249671</v>
+        <v>20.786162</v>
       </c>
       <c r="G40" t="n">
-        <v>187.2906710953828</v>
+        <v>188.4448194772872</v>
       </c>
       <c r="H40" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>70278.58195876658</v>
+        <v>24943.3944</v>
       </c>
       <c r="J40" t="n">
-        <v>86907.51155876658</v>
+        <v>41572.32399999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-287673.8306319989</v>
+        <v>-335317.3149545745</v>
       </c>
       <c r="L40" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M40" t="n">
-        <v>-3007312.601644107</v>
+        <v>-3052647.789202873</v>
       </c>
       <c r="N40" t="n">
-        <v>-2990683.672044107</v>
+        <v>-3036018.859602873</v>
       </c>
       <c r="O40" t="n">
-        <v>-3365265.014234872</v>
+        <v>-3412908.498557447</v>
       </c>
     </row>
     <row r="41">
@@ -2346,43 +2346,43 @@
         <v>101325</v>
       </c>
       <c r="C41" t="n">
-        <v>1.037608440913986e+32</v>
+        <v>3.664181406906491e+32</v>
       </c>
       <c r="D41" t="n">
-        <v>2.204185224214286e+31</v>
+        <v>3.664181406906491e+32</v>
       </c>
       <c r="E41" t="n">
-        <v>24.73633451427274</v>
+        <v>12.4716972</v>
       </c>
       <c r="F41" t="n">
-        <v>33.05079931427274</v>
+        <v>20.786162</v>
       </c>
       <c r="G41" t="n">
-        <v>188.1158573624695</v>
+        <v>188.9580841227939</v>
       </c>
       <c r="H41" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>71512.01073824374</v>
+        <v>25566.97926</v>
       </c>
       <c r="J41" t="n">
-        <v>88556.66357824374</v>
+        <v>42611.6321</v>
       </c>
       <c r="K41" t="n">
-        <v>-297080.8440148188</v>
+        <v>-344752.4403517276</v>
       </c>
       <c r="L41" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M41" t="n">
-        <v>-3006079.172864629</v>
+        <v>-3052024.204342873</v>
       </c>
       <c r="N41" t="n">
-        <v>-2989034.520024629</v>
+        <v>-3034979.551502873</v>
       </c>
       <c r="O41" t="n">
-        <v>-3374672.027617692</v>
+        <v>-3422343.623954601</v>
       </c>
     </row>
     <row r="42">
@@ -2393,43 +2393,43 @@
         <v>101325</v>
       </c>
       <c r="C42" t="n">
-        <v>1.133017605070979e+32</v>
+        <v>3.891710721616539e+32</v>
       </c>
       <c r="D42" t="n">
-        <v>2.497295582846944e+31</v>
+        <v>3.891710721616539e+32</v>
       </c>
       <c r="E42" t="n">
-        <v>24.86814210949518</v>
+        <v>12.4716972</v>
       </c>
       <c r="F42" t="n">
-        <v>33.18260690949518</v>
+        <v>20.786162</v>
       </c>
       <c r="G42" t="n">
-        <v>188.9252363038639</v>
+        <v>189.4589797337197</v>
       </c>
       <c r="H42" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>72752.14114289852</v>
+        <v>26190.56412</v>
       </c>
       <c r="J42" t="n">
-        <v>90212.51722289852</v>
+        <v>43650.9402</v>
       </c>
       <c r="K42" t="n">
-        <v>-306530.4790152156</v>
+        <v>-354212.9172408113</v>
       </c>
       <c r="L42" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M42" t="n">
-        <v>-3004839.042459975</v>
+        <v>-3051400.619482873</v>
       </c>
       <c r="N42" t="n">
-        <v>-2987378.666379975</v>
+        <v>-3033940.243402873</v>
       </c>
       <c r="O42" t="n">
-        <v>-3384121.662618089</v>
+        <v>-3431804.100843685</v>
       </c>
     </row>
     <row r="43">
@@ -2440,43 +2440,43 @@
         <v>101325</v>
       </c>
       <c r="C43" t="n">
-        <v>1.234874180107665e+32</v>
+        <v>4.127513133172181e+32</v>
       </c>
       <c r="D43" t="n">
-        <v>2.819224399376222e+31</v>
+        <v>4.127513133172181e+32</v>
       </c>
       <c r="E43" t="n">
-        <v>24.99553867637454</v>
+        <v>12.4716972</v>
       </c>
       <c r="F43" t="n">
-        <v>33.31000347637454</v>
+        <v>20.786162</v>
       </c>
       <c r="G43" t="n">
-        <v>189.7194670468949</v>
+        <v>189.9480884648285</v>
       </c>
       <c r="H43" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>73998.7514204435</v>
+        <v>26814.14898</v>
       </c>
       <c r="J43" t="n">
-        <v>91874.85074044351</v>
+        <v>44690.24829999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-316022.0034103806</v>
+        <v>-363698.1418993814</v>
       </c>
       <c r="L43" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M43" t="n">
-        <v>-3003592.43218243</v>
+        <v>-3050777.034622873</v>
       </c>
       <c r="N43" t="n">
-        <v>-2985716.33286243</v>
+        <v>-3032900.935302873</v>
       </c>
       <c r="O43" t="n">
-        <v>-3393613.187013254</v>
+        <v>-3441289.325502255</v>
       </c>
     </row>
     <row r="44">
@@ -2487,43 +2487,43 @@
         <v>101325</v>
       </c>
       <c r="C44" t="n">
-        <v>1.34347337917429e+32</v>
+        <v>4.371686555998549e+32</v>
       </c>
       <c r="D44" t="n">
-        <v>3.171870066964713e+31</v>
+        <v>4.371686555998549e+32</v>
       </c>
       <c r="E44" t="n">
-        <v>25.11858934559711</v>
+        <v>12.4716972</v>
       </c>
       <c r="F44" t="n">
-        <v>33.4330541455971</v>
+        <v>20.786162</v>
       </c>
       <c r="G44" t="n">
-        <v>190.4991608390515</v>
+        <v>190.4259523149491</v>
       </c>
       <c r="H44" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>75251.62256965128</v>
+        <v>27437.73384</v>
       </c>
       <c r="J44" t="n">
-        <v>93543.44512965129</v>
+        <v>45729.5564</v>
       </c>
       <c r="K44" t="n">
-        <v>-325554.708716262</v>
+        <v>-373207.538692888</v>
       </c>
       <c r="L44" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M44" t="n">
-        <v>-3002339.561033222</v>
+        <v>-3050153.449762873</v>
       </c>
       <c r="N44" t="n">
-        <v>-2984047.738473222</v>
+        <v>-3031861.627202873</v>
       </c>
       <c r="O44" t="n">
-        <v>-3403145.892319135</v>
+        <v>-3450798.722295761</v>
       </c>
     </row>
     <row r="45">
@@ -2534,43 +2534,43 @@
         <v>101325</v>
       </c>
       <c r="C45" t="n">
-        <v>1.459118320005746e+32</v>
+        <v>4.624327772295649e+32</v>
       </c>
       <c r="D45" t="n">
-        <v>3.557199712034015e+31</v>
+        <v>4.624327772295649e+32</v>
       </c>
       <c r="E45" t="n">
-        <v>25.23737598449098</v>
+        <v>12.4716972</v>
       </c>
       <c r="F45" t="n">
-        <v>33.55184078449098</v>
+        <v>20.786162</v>
       </c>
       <c r="G45" t="n">
-        <v>191.2648854619649</v>
+        <v>190.8930767372926</v>
       </c>
       <c r="H45" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>76510.5392805826</v>
+        <v>28061.3187</v>
       </c>
       <c r="J45" t="n">
-        <v>95218.0850805826</v>
+        <v>46768.8645</v>
       </c>
       <c r="K45" t="n">
-        <v>-335127.9072088384</v>
+        <v>-382740.5581589083</v>
       </c>
       <c r="L45" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M45" t="n">
-        <v>-3001080.644322291</v>
+        <v>-3049529.864902873</v>
       </c>
       <c r="N45" t="n">
-        <v>-2982373.098522291</v>
+        <v>-3030822.319102873</v>
       </c>
       <c r="O45" t="n">
-        <v>-3412719.090811712</v>
+        <v>-3460331.741761781</v>
       </c>
     </row>
     <row r="46">
@@ -2581,43 +2581,43 @@
         <v>101325</v>
       </c>
       <c r="C46" t="n">
-        <v>1.582120094746651e+32</v>
+        <v>4.885532470433434e+32</v>
       </c>
       <c r="D46" t="n">
-        <v>3.977249960074029e+31</v>
+        <v>4.885532470433434e+32</v>
       </c>
       <c r="E46" t="n">
-        <v>25.35199357272245</v>
+        <v>12.4716972</v>
       </c>
       <c r="F46" t="n">
-        <v>33.66645837272245</v>
+        <v>20.786162</v>
       </c>
       <c r="G46" t="n">
-        <v>192.0171690889427</v>
+        <v>191.3499338529319</v>
       </c>
       <c r="H46" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>77775.29067837895</v>
+        <v>28684.90356</v>
       </c>
       <c r="J46" t="n">
-        <v>96898.55971837895</v>
+        <v>47808.1726</v>
       </c>
       <c r="K46" t="n">
-        <v>-344740.9291861892</v>
+        <v>-392296.6752617435</v>
       </c>
       <c r="L46" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M46" t="n">
-        <v>-2999815.892924494</v>
+        <v>-3048906.280042873</v>
       </c>
       <c r="N46" t="n">
-        <v>-2980692.623884494</v>
+        <v>-3029783.011002873</v>
       </c>
       <c r="O46" t="n">
-        <v>-3422332.112789062</v>
+        <v>-3469887.858864617</v>
       </c>
     </row>
     <row r="47">
@@ -2628,43 +2628,43 @@
         <v>101325</v>
       </c>
       <c r="C47" t="n">
-        <v>1.712797838827038e+32</v>
+        <v>5.155395281224501e+32</v>
       </c>
       <c r="D47" t="n">
-        <v>4.434127697002515e+31</v>
+        <v>5.155395281224501e+32</v>
       </c>
       <c r="E47" t="n">
-        <v>25.46254712559173</v>
+        <v>12.4716972</v>
       </c>
       <c r="F47" t="n">
-        <v>33.77701192559172</v>
+        <v>20.786162</v>
       </c>
       <c r="G47" t="n">
-        <v>192.7565036741685</v>
+        <v>191.7969653186602</v>
       </c>
       <c r="H47" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>79045.67089982743</v>
+        <v>29308.48842</v>
       </c>
       <c r="J47" t="n">
-        <v>98584.66317982742</v>
+        <v>48847.4807</v>
       </c>
       <c r="K47" t="n">
-        <v>-354393.1204544685</v>
+        <v>-401875.3877988514</v>
       </c>
       <c r="L47" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M47" t="n">
-        <v>-2998545.512703046</v>
+        <v>-3048282.695182873</v>
       </c>
       <c r="N47" t="n">
-        <v>-2979006.520423046</v>
+        <v>-3028743.702902873</v>
       </c>
       <c r="O47" t="n">
-        <v>-3431984.304057342</v>
+        <v>-3479466.571401725</v>
       </c>
     </row>
     <row r="48">
@@ -2675,43 +2675,43 @@
         <v>101325</v>
       </c>
       <c r="C48" t="n">
-        <v>1.851478798974164e+32</v>
+        <v>5.434009812235146e+32</v>
       </c>
       <c r="D48" t="n">
-        <v>4.930010825591928e+31</v>
+        <v>5.434009812235146e+32</v>
       </c>
       <c r="E48" t="n">
-        <v>25.56914909636979</v>
+        <v>12.4716972</v>
       </c>
       <c r="F48" t="n">
-        <v>33.88361389636979</v>
+        <v>20.786162</v>
       </c>
       <c r="G48" t="n">
-        <v>193.483347947232</v>
+        <v>192.2345848928986</v>
       </c>
       <c r="H48" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>80321.4795283399</v>
+        <v>29932.07328</v>
       </c>
       <c r="J48" t="n">
-        <v>100276.1950483399</v>
+        <v>49886.78879999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-364083.840025017</v>
+        <v>-411476.2149429566</v>
       </c>
       <c r="L48" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M48" t="n">
-        <v>-2997269.704074533</v>
+        <v>-3047659.110322873</v>
       </c>
       <c r="N48" t="n">
-        <v>-2977314.988554534</v>
+        <v>-3027704.394802873</v>
       </c>
       <c r="O48" t="n">
-        <v>-3441675.02362789</v>
+        <v>-3489067.39854583</v>
       </c>
     </row>
     <row r="49">
@@ -2722,43 +2722,43 @@
         <v>101325</v>
       </c>
       <c r="C49" t="n">
-        <v>1.998498400433078e+32</v>
+        <v>5.721468680280168e+32</v>
       </c>
       <c r="D49" t="n">
-        <v>5.467149016593974e+31</v>
+        <v>5.721468680280168e+32</v>
       </c>
       <c r="E49" t="n">
-        <v>25.67191719516899</v>
+        <v>12.4716972</v>
       </c>
       <c r="F49" t="n">
-        <v>33.98638199516899</v>
+        <v>20.786162</v>
       </c>
       <c r="G49" t="n">
-        <v>194.1981300746393</v>
+        <v>192.6631807370192</v>
       </c>
       <c r="H49" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>81602.52190970967</v>
+        <v>30555.65814</v>
       </c>
       <c r="J49" t="n">
-        <v>101972.9606697097</v>
+        <v>50926.0969</v>
       </c>
       <c r="K49" t="n">
-        <v>-373812.4580131567</v>
+        <v>-421098.6959056969</v>
       </c>
       <c r="L49" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M49" t="n">
-        <v>-2995988.661693164</v>
+        <v>-3047035.525462873</v>
       </c>
       <c r="N49" t="n">
-        <v>-2975618.222933163</v>
+        <v>-3026665.086702873</v>
       </c>
       <c r="O49" t="n">
-        <v>-3451403.64161603</v>
+        <v>-3498689.87950857</v>
       </c>
     </row>
     <row r="50">
@@ -2769,43 +2769,43 @@
         <v>101325</v>
       </c>
       <c r="C50" t="n">
-        <v>2.154200313457744e+32</v>
+        <v>6.017863542233226e+32</v>
       </c>
       <c r="D50" t="n">
-        <v>6.047864454286573e+31</v>
+        <v>6.017863542233226e+32</v>
       </c>
       <c r="E50" t="n">
-        <v>25.77097256809781</v>
+        <v>12.4716972</v>
       </c>
       <c r="F50" t="n">
-        <v>34.08543736809781</v>
+        <v>20.786162</v>
       </c>
       <c r="G50" t="n">
-        <v>194.9012500399423</v>
+        <v>193.0831174841597</v>
       </c>
       <c r="H50" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>82888.6093680402</v>
+        <v>31179.243</v>
       </c>
       <c r="J50" t="n">
-        <v>103674.7713680402</v>
+        <v>51965.405</v>
       </c>
       <c r="K50" t="n">
-        <v>-383578.3537318155</v>
+        <v>-430742.3887103994</v>
       </c>
       <c r="L50" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M50" t="n">
-        <v>-2994702.574234833</v>
+        <v>-3046411.940602873</v>
       </c>
       <c r="N50" t="n">
-        <v>-2973916.412234833</v>
+        <v>-3025625.778602873</v>
       </c>
       <c r="O50" t="n">
-        <v>-3461169.537334689</v>
+        <v>-3508333.572313272</v>
       </c>
     </row>
     <row r="51">
@@ -2816,43 +2816,43 @@
         <v>101325</v>
       </c>
       <c r="C51" t="n">
-        <v>2.318936519125409e+32</v>
+        <v>6.323285124272578e+32</v>
       </c>
       <c r="D51" t="n">
-        <v>6.674552576245437e+31</v>
+        <v>6.323285124272578e+32</v>
       </c>
       <c r="E51" t="n">
-        <v>25.86643828660196</v>
+        <v>12.4716972</v>
       </c>
       <c r="F51" t="n">
-        <v>34.18090308660195</v>
+        <v>20.786162</v>
       </c>
       <c r="G51" t="n">
-        <v>195.5930817857532</v>
+        <v>193.4947381031637</v>
       </c>
       <c r="H51" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>84179.55933858255</v>
+        <v>31802.82786</v>
       </c>
       <c r="J51" t="n">
-        <v>105381.4445785826</v>
+        <v>53004.71309999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-393380.9139750881</v>
+        <v>-440406.8690630675</v>
       </c>
       <c r="L51" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M51" t="n">
-        <v>-2993411.624264291</v>
+        <v>-3045788.355742873</v>
       </c>
       <c r="N51" t="n">
-        <v>-2972209.739024291</v>
+        <v>-3024586.470502873</v>
       </c>
       <c r="O51" t="n">
-        <v>-3470972.097577961</v>
+        <v>-3517998.052665941</v>
       </c>
     </row>
     <row r="52">
@@ -2863,43 +2863,43 @@
         <v>101325</v>
       </c>
       <c r="C52" t="n">
-        <v>2.49306737451925e+32</v>
+        <v>6.637823249671171e+32</v>
       </c>
       <c r="D52" t="n">
-        <v>7.349682807206054e+31</v>
+        <v>6.637823249671171e+32</v>
       </c>
       <c r="E52" t="n">
-        <v>25.95843810274305</v>
+        <v>12.4716972</v>
       </c>
       <c r="F52" t="n">
-        <v>34.27290290274305</v>
+        <v>20.786162</v>
       </c>
       <c r="G52" t="n">
-        <v>196.2739751538867</v>
+        <v>193.8983655815194</v>
       </c>
       <c r="H52" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>85475.19543186096</v>
+        <v>32426.41272</v>
       </c>
       <c r="J52" t="n">
-        <v>107092.803911861</v>
+        <v>54044.0212</v>
       </c>
       <c r="K52" t="n">
-        <v>-403219.5314882443</v>
+        <v>-450091.7293119504</v>
       </c>
       <c r="L52" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M52" t="n">
-        <v>-2992115.988171012</v>
+        <v>-3045164.770882873</v>
       </c>
       <c r="N52" t="n">
-        <v>-2970498.379691012</v>
+        <v>-3023547.162402873</v>
       </c>
       <c r="O52" t="n">
-        <v>-3480810.715091118</v>
+        <v>-3527682.912914824</v>
       </c>
     </row>
     <row r="53">
@@ -2910,43 +2910,43 @@
         <v>101325</v>
       </c>
       <c r="C53" t="n">
-        <v>2.676961677317939e+32</v>
+        <v>6.961566865230591e+32</v>
       </c>
       <c r="D53" t="n">
-        <v>8.075799286934022e+31</v>
+        <v>6.961566865230591e+32</v>
       </c>
       <c r="E53" t="n">
-        <v>26.04709543159955</v>
+        <v>12.4716972</v>
       </c>
       <c r="F53" t="n">
-        <v>34.36156023159955</v>
+        <v>20.786162</v>
       </c>
       <c r="G53" t="n">
-        <v>196.9442576539568</v>
+        <v>194.2943044479878</v>
       </c>
       <c r="H53" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>86775.34744139141</v>
+        <v>33049.99758</v>
       </c>
       <c r="J53" t="n">
-        <v>108808.6791613914</v>
+        <v>55083.3293</v>
       </c>
       <c r="K53" t="n">
-        <v>-413093.603621594</v>
+        <v>-459796.5774871676</v>
       </c>
       <c r="L53" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M53" t="n">
-        <v>-2990815.836161482</v>
+        <v>-3044541.186022873</v>
       </c>
       <c r="N53" t="n">
-        <v>-2968782.504441482</v>
+        <v>-3022507.854302873</v>
       </c>
       <c r="O53" t="n">
-        <v>-3490684.787224467</v>
+        <v>-3537387.761090041</v>
       </c>
     </row>
     <row r="54">
@@ -2957,43 +2957,43 @@
         <v>101325</v>
       </c>
       <c r="C54" t="n">
-        <v>2.870996729825363e+32</v>
+        <v>7.294604066449749e+32</v>
       </c>
       <c r="D54" t="n">
-        <v>8.855521592063692e+31</v>
+        <v>7.294604066449749e+32</v>
       </c>
       <c r="E54" t="n">
-        <v>26.13253252693397</v>
+        <v>12.4716972</v>
       </c>
       <c r="F54" t="n">
-        <v>34.44699732693397</v>
+        <v>20.786162</v>
       </c>
       <c r="G54" t="n">
-        <v>197.6042360857606</v>
+        <v>194.682842152904</v>
       </c>
       <c r="H54" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>88079.85130548342</v>
+        <v>33673.58244</v>
       </c>
       <c r="J54" t="n">
-        <v>110528.9062654834</v>
+        <v>56122.63739999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-423002.5311660702</v>
+        <v>-469521.0364128407</v>
       </c>
       <c r="L54" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M54" t="n">
-        <v>-2989511.33229739</v>
+        <v>-3043917.601162873</v>
       </c>
       <c r="N54" t="n">
-        <v>-2967062.27733739</v>
+        <v>-3021468.546202873</v>
       </c>
       <c r="O54" t="n">
-        <v>-3500593.714768943</v>
+        <v>-3547112.220015714</v>
       </c>
     </row>
     <row r="55">
@@ -3004,43 +3004,43 @@
         <v>101325</v>
       </c>
       <c r="C55" t="n">
-        <v>3.075558402469267e+32</v>
+        <v>7.637022121511482e+32</v>
       </c>
       <c r="D55" t="n">
-        <v>9.691545451899244e+31</v>
+        <v>7.637022121511482e+32</v>
       </c>
       <c r="E55" t="n">
-        <v>26.21486982073884</v>
+        <v>12.4716972</v>
       </c>
       <c r="F55" t="n">
-        <v>34.52933462073884</v>
+        <v>20.786162</v>
       </c>
       <c r="G55" t="n">
-        <v>198.2541980365411</v>
+        <v>195.0642503218215</v>
       </c>
       <c r="H55" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>89388.54903203575</v>
+        <v>34297.1673</v>
       </c>
       <c r="J55" t="n">
-        <v>112253.3272320358</v>
+        <v>57161.9455</v>
       </c>
       <c r="K55" t="n">
-        <v>-432945.7173684523</v>
+        <v>-479264.7428850092</v>
       </c>
       <c r="L55" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M55" t="n">
-        <v>-2988202.634570837</v>
+        <v>-3043294.016302873</v>
       </c>
       <c r="N55" t="n">
-        <v>-2965337.856370837</v>
+        <v>-3020429.238102873</v>
       </c>
       <c r="O55" t="n">
-        <v>-3510536.900971326</v>
+        <v>-3556855.926487883</v>
       </c>
     </row>
     <row r="56">
@@ -3051,43 +3051,43 @@
         <v>101325</v>
       </c>
       <c r="C56" t="n">
-        <v>3.291041196793759e+32</v>
+        <v>7.98890749416342e+32</v>
       </c>
       <c r="D56" t="n">
-        <v>1.058664345819956e+32</v>
+        <v>7.98890749416342e+32</v>
       </c>
       <c r="E56" t="n">
-        <v>26.29422540125774</v>
+        <v>12.4716972</v>
       </c>
       <c r="F56" t="n">
-        <v>34.60869020125774</v>
+        <v>20.786162</v>
       </c>
       <c r="G56" t="n">
-        <v>198.8944132706208</v>
+        <v>195.4387858961981</v>
       </c>
       <c r="H56" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>90701.28859386961</v>
+        <v>34920.75216</v>
       </c>
       <c r="J56" t="n">
-        <v>113981.7900338696</v>
+        <v>58201.2536</v>
       </c>
       <c r="K56" t="n">
-        <v>-442922.5671238686</v>
+        <v>-489027.3469093547</v>
       </c>
       <c r="L56" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M56" t="n">
-        <v>-2986889.895009004</v>
+        <v>-3042670.431442873</v>
       </c>
       <c r="N56" t="n">
-        <v>-2963609.393569004</v>
+        <v>-3019389.930002873</v>
       </c>
       <c r="O56" t="n">
-        <v>-3520513.750726742</v>
+        <v>-3566618.530512228</v>
       </c>
     </row>
     <row r="57">
@@ -3098,43 +3098,43 @@
         <v>101325</v>
       </c>
       <c r="C57" t="n">
-        <v>3.517848307967508e+32</v>
+        <v>8.350345865563143e+32</v>
       </c>
       <c r="D57" t="n">
-        <v>1.154366576899003e+32</v>
+        <v>8.350345865563143e+32</v>
       </c>
       <c r="E57" t="n">
-        <v>26.37071460760064</v>
+        <v>12.4716972</v>
       </c>
       <c r="F57" t="n">
-        <v>34.68517940760064</v>
+        <v>20.786162</v>
       </c>
       <c r="G57" t="n">
-        <v>199.5251350258253</v>
+        <v>195.8066921731178</v>
       </c>
       <c r="H57" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>92017.92380096215</v>
+        <v>35544.33702</v>
       </c>
       <c r="J57" t="n">
-        <v>115714.1484809621</v>
+        <v>59240.5617</v>
       </c>
       <c r="K57" t="n">
-        <v>-452932.4863426398</v>
+        <v>-498808.5109933856</v>
       </c>
       <c r="L57" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M57" t="n">
-        <v>-2985573.259801911</v>
+        <v>-3042046.846582873</v>
       </c>
       <c r="N57" t="n">
-        <v>-2961877.035121911</v>
+        <v>-3018350.621902873</v>
       </c>
       <c r="O57" t="n">
-        <v>-3530523.669945513</v>
+        <v>-3576399.694596259</v>
       </c>
     </row>
     <row r="58">
@@ -3145,43 +3145,43 @@
         <v>101325</v>
       </c>
       <c r="C58" t="n">
-        <v>3.756391686826729e+32</v>
+        <v>8.721422155152119e+32</v>
       </c>
       <c r="D58" t="n">
-        <v>1.256554080646131e+32</v>
+        <v>8.721422155152119e+32</v>
       </c>
       <c r="E58" t="n">
-        <v>26.44444972216731</v>
+        <v>12.4716972</v>
       </c>
       <c r="F58" t="n">
-        <v>34.75891452216731</v>
+        <v>20.786162</v>
       </c>
       <c r="G58" t="n">
-        <v>200.1466012284954</v>
+        <v>196.168199754589</v>
       </c>
       <c r="H58" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>93338.3141549282</v>
+        <v>36167.92188</v>
       </c>
       <c r="J58" t="n">
-        <v>117450.2620749282</v>
+        <v>60279.8698</v>
       </c>
       <c r="K58" t="n">
-        <v>-462974.8814877084</v>
+        <v>-508607.909488308</v>
       </c>
       <c r="L58" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M58" t="n">
-        <v>-2984252.869447945</v>
+        <v>-3041423.261722873</v>
       </c>
       <c r="N58" t="n">
-        <v>-2960140.921527945</v>
+        <v>-3017311.313802873</v>
       </c>
       <c r="O58" t="n">
-        <v>-3540566.065090582</v>
+        <v>-3586199.093091181</v>
       </c>
     </row>
     <row r="59">
@@ -3192,43 +3192,43 @@
         <v>101325</v>
       </c>
       <c r="C59" t="n">
-        <v>4.007092101469903e+32</v>
+        <v>9.102220540617843e+32</v>
       </c>
       <c r="D59" t="n">
-        <v>1.365527594902855e+32</v>
+        <v>9.102220540617843e+32</v>
       </c>
       <c r="E59" t="n">
-        <v>26.51553974479561</v>
+        <v>12.4716972</v>
       </c>
       <c r="F59" t="n">
-        <v>34.83000454479561</v>
+        <v>20.786162</v>
       </c>
       <c r="G59" t="n">
-        <v>200.7590356366482</v>
+        <v>196.5235274156936</v>
       </c>
       <c r="H59" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>94662.32469022828</v>
+        <v>36791.50674</v>
       </c>
       <c r="J59" t="n">
-        <v>119189.9958502283</v>
+        <v>61319.1779</v>
       </c>
       <c r="K59" t="n">
-        <v>-473049.1592778839</v>
+        <v>-518425.2279762961</v>
       </c>
       <c r="L59" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M59" t="n">
-        <v>-2982928.858912645</v>
+        <v>-3040799.676862873</v>
       </c>
       <c r="N59" t="n">
-        <v>-2958401.187752645</v>
+        <v>-3016272.005702873</v>
       </c>
       <c r="O59" t="n">
-        <v>-3550640.342880757</v>
+        <v>-3596016.411579169</v>
       </c>
     </row>
     <row r="60">
@@ -3239,43 +3239,43 @@
         <v>101325</v>
       </c>
       <c r="C60" t="n">
-        <v>4.270379198419221e+32</v>
+        <v>9.492824476998952e+32</v>
       </c>
       <c r="D60" t="n">
-        <v>1.481595821763452e+32</v>
+        <v>9.492824476998952e+32</v>
       </c>
       <c r="E60" t="n">
-        <v>26.58409023490167</v>
+        <v>12.4716972</v>
       </c>
       <c r="F60" t="n">
-        <v>34.89855503490167</v>
+        <v>20.786162</v>
       </c>
       <c r="G60" t="n">
-        <v>201.3626489189422</v>
+        <v>196.8728828997711</v>
       </c>
       <c r="H60" t="n">
-        <v>26404.67143400882</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>95989.82580583653</v>
+        <v>37415.0916</v>
       </c>
       <c r="J60" t="n">
-        <v>120933.2202058365</v>
+        <v>62358.486</v>
       </c>
       <c r="K60" t="n">
-        <v>-483154.72655099</v>
+        <v>-528260.1626993131</v>
       </c>
       <c r="L60" t="n">
         <v>-1.172192414246</v>
       </c>
       <c r="M60" t="n">
-        <v>-2981601.357797037</v>
+        <v>-3040176.092002873</v>
       </c>
       <c r="N60" t="n">
-        <v>-2956657.963397037</v>
+        <v>-3015232.697602873</v>
       </c>
       <c r="O60" t="n">
-        <v>-3560745.910153863</v>
+        <v>-3605851.346302186</v>
       </c>
     </row>
   </sheetData>
